--- a/medford_rinolaringoskopy.xlsx
+++ b/medford_rinolaringoskopy.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Риноларингоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Aohua, Olympus, Pentax — всего 20 позиций.</t>
+          <t>Риноларингоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Aohua, Olympus, Pentax.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_rinolaringoskopy.xlsx
+++ b/medford_rinolaringoskopy.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать риноларингоскопы для клиники?</t>
+          <t>Чем фиброскоп отличается от видеориноскопа?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Диаметр вводимой трубки, мм, Рабочая длина, мм, Угол поля зрения, °, Диаметр дистального конца, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Фиброскоп передаёт изображение по пучку оптических волокон в окуляр, врач смотрит глазом. Видеориноскоп несёт видеоматрицу на дистальном конце и выводит картинку на монитор через процессор. Видеоскоп удобнее для документирования, записи и показа, фиброскоп проще и не требует стойки.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какой диаметр выбрать для детского приёма?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Для детей и узких носовых ходов берут ультратонкие модели: в каталоге есть трубки диаметром 2,2–2,9 мм и дистальный конец от 1,8 мм. Тонкий эндоскоп проходит комфортнее и меньше травмирует слизистую. Конкретную модель под пациента и метод подбирает врач.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Подойдёт ли риноларингоскоп к моему процессору?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Aohua, Olympus, Pentax. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Совместимость зависит от бренда, поколения процессора и типа коннектора. Видеоскопы Olympus, Pentax и Aohua рассчитаны на свои или совместимые видеосистемы. До покупки сообщите модель имеющегося процессора и источника света — мы сверим разъём и стандарт, чтобы не докупать стойку.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Нужно ли регистрационное удостоверение Росздравнадзора?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Да. Риноларингоскоп — медицинское изделие, для легального применения в клинике нужно действующее регистрационное удостоверение Росздравнадзора. Наличие и реквизиты РУ уточняйте до покупки; без него прибор нельзя использовать в лицензируемой медицинской деятельности, даже если он полностью исправен и укомплектован.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Что означает угол поля зрения и глубина резкости?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Угол поля зрения (в каталоге 75–120°) — ширина охвата картинки за один проход: чем больше, тем больше структур видно. Глубина резкости (например, 2–50 или 5–50 мм) показывает диапазон дистанций до слизистой, на котором изображение остаётся чётким без перефокусировки.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Какая рабочая длина нужна для осмотра гортани?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Для амбулаторного осмотра носоглотки и гортани обычно достаточно рабочей длины 300 мм — это большинство моделей каталога. Удлинённые версии 450–600 мм применяют для интубационных и глубоких задач, где инструмент проходит дальше по дыхательным путям. Выбор длины под конкретную методику и пациента определяет врач.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>rinolaringoskopy</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Предоставляете ли гарантию и сервис?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>На поставляемое оборудование распространяется гарантия, а обслуживание и ремонт риноларингоскопов выполняет собственный инженерный сервис. Условия по конкретной модели, срок гарантии и порядок обращения уточняйте у менеджера при оформлении. Для гибких эндоскопов отдельно оговаривают проверку герметичности канала и состояния изгибаемой части.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>rinolaringoskopy</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2072,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Риноларингоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Aohua, Olympus, Pentax.</t>
+          <t>Риноларингоскопы — это гибкие эндоскопы для осмотра полости носа, носоглотки и гортани через естественные пути. В каталоге представлены фиброскопы и видеоскопы Olympus (серия ENF), Pentax (линейки FNL и VNL), Aohua (MBC, VRL) и другие модели. Диаметр вводимой трубки варьируется от 2,2 до 5,7 мм, рабочая длина — от 300 до 600 мм, угол поля зрения — от 75 до 120°. Ультратонкие версии с дистальным концом 1,8–2,6 мм подходят для педиатрии и узких носовых ходов.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2356,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Фиброскоп и видеориноскоп: сравнение</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2644,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое риноларингоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4658,251 +4734,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Фиброскоп и видеориноскоп: сравнение</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Признак</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Риноларингофиброскоп</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Диаметр вводимой трубки, мм</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Рабочая длина, мм</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Угол поля зрения, °</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Диаметр дистального конца, мм</t>
+          <t>Видеориноларингоскоп</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Видеоларингоскоп Aohua MBC-6</t>
+          <t>Передача изображения</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Aohua</t>
+          <t>Волоконный световод в окуляр</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>5.8</t>
+          <t>Матрица на дистальном конце на монитор</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Риноларингоскоп Olympus ENF-V3</t>
+          <t>Документирование</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>Через насадку-камеру</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2,9</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>90°</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>2,6</t>
+          <t>Штатно, запись и трансляция</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Риноларинговидеоскоп Olympus ENF-V2</t>
+          <t>Потребность в стойке</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>Внешний осветитель</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>3,4</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>90°</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>3,3</t>
+          <t>Видеопроцессор и источник света</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Видеоларингоскоп Aohua VRL-Q30</t>
+          <t>Вес и цена парка</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Aohua</t>
+          <t>Легче и дешевле</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>4.9</t>
+          <t>Выше за счёт видеосистемы</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Видеоларингоскоп Aohua MBC-5</t>
+          <t>Пример моделей</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Aohua</t>
+          <t>Olympus ENF-P4, Pentax FNL-7RP3</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Видеоларингоскоп Aohua VRL-1T30</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Aohua</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>5.8</t>
+          <t>Olympus ENF-V3, Aohua VRL-Q30</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4914,7 +4865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5240,12 +5191,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите диаметр вводимой трубки</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается риноларингоскопы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Диаметр задаёт проходимость и комфорт пациента. В каталоге трубки от 2,2 до 5,7 мм: тонкие (2,2–2,9 мм) берут для детей и узких носовых ходов, средние (3,4–4,0 мм) — для универсального взрослого приёма, толстые дают рабочий канал для манипуляций. Дистальный конец бывает даже 1,8 мм.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5285,12 +5236,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите тип: фиброскоп или видеоскоп</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Фиброскоп передаёт изображение по волоконному световоду в окуляр, он легче и проще в парке. Видеоскоп несёт матрицу на дистальном конце и выводит картинку на монитор, что удобно для документирования и обучения. Выбор зависит от того, нужен ли вывод на экран и запись.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5330,12 +5281,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Сопоставьте рабочую длину с задачами</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Диаметр вводимой трубки, мм, Рабочая длина, мм, Угол поля зрения, °, Диаметр дистального конца, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Рабочая длина в каталоге — от 300 до 600 мм. Стандартные 300 мм закрывают осмотр носоглотки и гортани на амбулаторном приёме. Удлинённые до 450–600 мм нужны для интубационных и специфических задач, где инструмент проходит глубже по дыхательным путям.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5375,12 +5326,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените угол поля зрения и глубину резкости</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Aohua, Olympus, Pentax.</t>
+          <t>Угол поля зрения у моделей каталога — от 75 до 120°: широкий угол охватывает больше структур за один проход. Глубина резкости (диапазоны 2–50, 3–50, 5–50 мм) определяет, насколько картинка остаётся чёткой при изменении дистанции до слизистой.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5420,12 +5371,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Проверьте совместимость с процессором и светом</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Видеоскоп работает в связке с видеопроцессором и источником света своего или совместимого стандарта. До покупки уточните разъём, поколение процессора и тип коннектора, иначе к аппарату придётся докупать стойку. Фиброскоп требует внешний осветитель под свой байонет.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5465,12 +5416,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните комплектность и регистрацию</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Запросите наличие регистрационного удостоверения Росздравнадзора, комплект транспортировки и герметичность канала для обработки. Уточните состояние изгибаемой части и оптики, наличие клапанов, заглушек и адаптеров. Эти позиции определяют готовность прибора к работе и корректной дезинфекции; для видеоскопа отдельно проверяют разъём и совместимость с процессором.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5520,7 +5471,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Риноларингоскопы подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Aohua, Olympus, Pentax. При выборе обращают внимание на диаметр вводимой трубки, рабочая длина, угол поля зрения, диаметр дистального конца, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>При подборе риноларингоскопа я в первую очередь смотрю на диаметр вводимой трубки и задачи приёма. Для детей и узких носовых ходов берут ультратонкие модели от 2,2 до 2,9 мм, для взрослого потока подойдёт трубка около 3,4–4,0 мм. Фиброскоп проще и дешевле в парке, видеоскоп даёт картинку на монитор и удобен для документирования. Совместимость с имеющимся процессором и источником света я проверяю до сделки, чтобы не докупать стойку.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5804,13 +5755,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое риноларингоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Риноларингоскопы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Aohua, Olympus, Pentax. Подберём вариант под задачи вашего отделения.</t>
+          <t>Риноларингоскоп — гибкий эндоскоп для осмотра носа, носоглотки и гортани. Различают фиброскопы, где картинка идёт по световоду в окуляр, и видеоскопы с матрицей на дистальном конце и выводом на монитор. Ключевые параметры выбора: диаметр вводимой трубки (в каталоге от 2,2 до 5,7 мм), рабочая длина (300–600 мм), угол поля зрения (75–120°) и глубина резкости. Тонкие модели удобны для детей, толстые дают рабочий канал. Совместимость с процессором и источником света уточняют до покупки.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5847,13 +5798,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое риноларингоскоп</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Диаметр вводимой трубки, мм, Рабочая длина, мм, Угол поля зрения, °, Диаметр дистального конца, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Риноларингоскоп — гибкий эндоскоп для эндоскопического осмотра верхних дыхательных путей: полости носа, носоглотки, гортани и голосовых связок. Инструмент вводят через естественные пути, изгибаемый дистальный конец позволяет обойти анатомические изгибы. Прибор применяют в оториноларингологии для диагностики воспалений, полипов, новообразований и функциональной оценки.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5890,13 +5841,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Фиброскоп и видеоскоп: в чём разница</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Волоконный риноларингофиброскоп передаёт изображение по световоду в окуляр — это компактное и недорогое решение. Видеориноскоп несёт CMOS/CCD-матрицу на дистальном конце и выводит картинку на монитор через видеопроцессор. Второй вариант даёт документирование и трансляцию, но требует совместимой видеостойки и источника света.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5933,13 +5884,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Ключевые характеристики при подборе</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Основные параметры: диаметр вводимой трубки (в каталоге 2,2–5,7 мм), диаметр дистального конца (от 1,8 мм), рабочая длина (300–600 мм), угол поля зрения (75–120°) и глубина резкости. Тонкие модели предназначены для педиатрии и узких ходов, толстые несут рабочий канал для инструментов и аспирации.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5956,6 +5907,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Бренды и модельные линейки</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>В каталоге собраны риноларингоскопы Olympus (серия ENF: ENF-V3, ENF-VH, ENF-XP и другие), Pentax (фиброскопы FNL-7RP3, FNL-10RP3 и видеоскопы VNL), Aohua (MBC, VRL) и отечественные решения. Модели различаются оптикой, диаметром и наличием рабочего канала, что покрывает и амбулаторные, и специализированные задачи.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>rinolaringoskopy</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
